--- a/outputs/Ergebnisse.xlsx
+++ b/outputs/Ergebnisse.xlsx
@@ -5206,53 +5206,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Zeitpunkt</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Geschlecht</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Alter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>M45</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>score_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>zeitpunkt</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>geschlecht</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>alter</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>M05</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>M06</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>M45</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
@@ -5300,6 +5305,7 @@
       <c r="I2" t="n">
         <v>251</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5345,6 +5351,7 @@
       <c r="I3" t="n">
         <v>251</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5390,6 +5397,7 @@
       <c r="I4" t="n">
         <v>212</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5435,13 +5443,10 @@
       <c r="I5" t="n">
         <v>195</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>* p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -5450,6 +5455,11 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>* p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Ergebnisse.xlsx
+++ b/outputs/Ergebnisse.xlsx
@@ -5206,7 +5206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5255,11 +5255,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>score_type</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5302,10 +5297,11 @@
           <t>0.3362</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5348,10 +5344,11 @@
           <t>0.5527</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>251</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5394,10 +5391,11 @@
           <t>-8.5505</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>212</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5440,13 +5438,20 @@
           <t>0.1451**</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>195</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>* p&lt;0.05,
+** p&lt;0.01,
+*** p&lt;0.001</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -5455,11 +5460,6 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>* p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Ergebnisse.xlsx
+++ b/outputs/Ergebnisse.xlsx
@@ -16,7 +16,8 @@
     <sheet name="Scoreverteilung" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ANOVA Diagnose" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Multivariate Regressionsanalyse" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Modelldiagnostik" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Interaktionsterm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Konfundierung" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,136 +528,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A11:H14"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AIC_Interaktion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>AIC_Ohne_Interaktion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AIC_Differenz</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Interaktion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vasa</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1950.19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1953.01</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vasp</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1970.74</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1972.37</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ffbh</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3436.67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3435.27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-312.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-311.46</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Koeffizient_Ohne_Diagnose</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Koeffizient_Mit_Diagnose</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Änderung_Koeffizient_%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SE_Ohne_Diagnose</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SE_Mit_Diagnose</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Änderung_SE_%</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Konfundierung</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Zeitpunkt</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B2" t="n">
         <v>-0.1694</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C2" t="n">
         <v>-0.1694</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F2" t="n">
         <v>0.01</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Geschlecht</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B3" t="n">
         <v>-0.0048</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C3" t="n">
         <v>-0.0488</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D3" t="n">
         <v>924.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E3" t="n">
         <v>0.031</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F3" t="n">
         <v>0.0295</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Alter</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B4" t="n">
         <v>0.0002</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C4" t="n">
         <v>0.0019</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D4" t="n">
         <v>878.9</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E4" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F4" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G4" t="n">
         <v>3.6</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
@@ -5447,9 +5573,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>* p&lt;0.05,
-** p&lt;0.01,
-*** p&lt;0.001</t>
+          <t>* p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
